--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_04_Full_88_Cau/Day_04_Ngan_Hang_Phan_04_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_04_Full_88_Cau/Day_04_Ngan_Hang_Phan_04_22_Cau.xlsx
@@ -691,7 +691,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định bằng chứng nào nhìn thấy được lời gọi tool và hành động thực thi, không chỉ đầu ra cuối.</t>
+          <t>Để kiểm chứng tiêu chí agent không được gọi `send_refund` trước khi có bản ghi xác nhận hợp lệ, bài đánh giá phải là Agent eval kiểm tra tool-call trace, trạng thái xác nhận và các hành động thực thi, chứ không chỉ chấm text đầu ra cuối.</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách chỉ số mục tiêu khỏi ranh giới không được phép hồi quy.</t>
+          <t>Phiên bản v2 tuy tăng điểm tổng từ 80 lên 86 nhưng điểm an toàn bị hồi quy từ 20/20 xuống 15/20. Tiêu chí an toàn là ranh giới cứng không được phép hồi quy, nên quyết định đúng là không đưa lên production, rollback về v1 và điều tra nguyên nhân hồi quy an toàn.</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đi từ điểm số ngược về nội dung chính xác/cấu hình/sự kiện khi chạy.</t>
+          <t>Bản ghi điểm hỗ trợ kiểm tra và rollback phải liên kết đầy đủ: Hash prompt (a), Hash khai báo tool (b), Hash bộ case eval (c), Cấu hình provider/model (d), và Đầu ra thô kèm trace tool/hội thoại (e).</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy hỏi model/harness đã thực sự có cơ hội thực hiện tác vụ chưa.</t>
+          <t>Các lần chạy là lỗi hạ tầng chứ không phải lỗi mô hình/prompt: API key không hợp lệ 401 (a), Bị rate-limit 429 không có completion (b), Lỗi DNS endpoint (d), và Bị từ chối quyền truy cập model (f). Chọn sai tool (c) hay vi phạm format (e) là lỗi của mô hình/prompt.</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách thành phần hệ thống được kiểm trong mock khỏi thành phần chưa chạy.</t>
+          <t>Mock test 100/100 pass chỉ chứng minh các đường đi logic và harness của mã nguồn hoạt động đúng; nó chưa chứng minh mô hình thật sẽ sinh đúng và ổn định trên dữ liệu thực tế.</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Liệt kê điều kiện làm thay đổi quyết định có/không của chính hành động giữ phòng.</t>
+          <t>Gói thông tin vừa tối thiểu vừa đủ để thực hiện hành động giữ phòng Hotel A: Hotel A, ngày ở, tình trạng phòng/giá còn hiệu lực, ngân sách, sự cho phép giữ phòng của người dùng, cùng nguồn và thời điểm thu thập.</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đánh giá tác động, dữ liệu, khả năng đảo ngược và hậu quả; bỏ qua đặc điểm trình bày.</t>
+          <t>Các thuộc tính làm rủi ro tăng mạnh và cần kiểm soát nghiêm ngặt: Có thay đổi dữ liệu/gửi ra ngoài (a), Dữ liệu nhạy cảm sức khỏe (b), Khó thu hồi sau khi gửi (c), và Có hậu quả trực tiếp tới người nhận thật (e). Độ dài tên hàm (d) hay số câu (f) không ảnh hưởng rủi ro.</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm ranh giới chưa được đo, không đếm số câu hoặc tên thực thể.</t>
+          <t>Để tăng độ bao phủ kiểm tra khi bộ test chưa đo phản hồi không dùng tool và chưa đo ranh giới ghi dữ liệu của enroll_course, sửa đổi tối thiểu là thay case trùng H2 bằng case không dùng tool, và thay H4 bằng ca đăng ký chưa xác nhận (kỳ vọng không ghi dữ liệu).</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ giữ một biến thay đổi ở mỗi lần so sánh.</t>
+          <t>Để cô lập nguyên nhân khi cả prompt và schema tool cùng đổi, các bước kiểm tra có kiểm soát gồm: Ghi lại artifact chính xác và trace (a), Test riêng implementation tool với đối số hợp lệ (b), Chạy prompt mới với schema cũ đã biết tốt (c), và Chạy prompt cũ với schema mới (e).</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy hỏi: kiểm soát có còn đúng nếu model bỏ qua chỉ dẫn không?</t>
+          <t>Khi mô hình tự ý tạo tool call `refund` và tự bịa text `user confirmed`, lớp chịu trách nhiệm chặn thực thi bắt buộc phải là Harness/Execution Guardrail bằng cách kiểm tra trạng thái xác nhận thực tế trên server trước khi dispatch lệnh gọi.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_04_Full_88_Cau/Day_04_Ngan_Hang_Phan_04_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_04_Full_88_Cau/Day_04_Ngan_Hang_Phan_04_22_Cau.xlsx
@@ -776,10 +776,22 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Chỉ kết luận khi biết schema thực tế được đưa cho model.
-Phân tích theo nguyên lý thiết kế: Chỉ kết luận khi biết schema thực tế được đưa cho model.</t>
+- 1.0 điểm: Xác định đúng lỗi nằm ở khâu giao tiếp tên trường giữa mô hình và tool schema (`course` vs `course_code`).
+- 1.0 điểm: Xác nhận lớp backend/hàm thực thi hoàn toàn không có lỗi (dựa trên bằng chứng gọi trực tiếp pass).
+- 1.0 điểm: Nêu rõ bằng chứng về JSON Schema thực tế truyền vào API request cho mô hình tại runtime.
+- 1.0 điểm: Nêu rõ bằng chứng kiểm tra sự tồn tại của ví dụ cũ/bias trong system prompt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xác định Lớp lỗi (Failure Layer Localization):
+- Lớp lỗi chính: Lớp Định nghĩa Lược đồ Công cụ (Tool Schema Definition / Tool Interface Layer) hoặc Lớp Hướng dẫn Mô hình (Prompting / In-context Few-shot Layer).
+- Bản chất sự cố: Mô hình đã trích xuất đúng giá trị 'CS101' từ prompt, và hàm backend `lookup_course(course_code='CS101')` hoạt động hoàn hảo. Lỗi xuất hiện ở khâu giao tiếp trung gian: Mô hình sinh ra tên tham số là `course` thay vì `course_code` theo yêu cầu của dispatcher.
+2. Bằng chứng cần bổ sung trước khi kết luận chắc chắn nguyên nhân gốc rễ (Root Cause):
+- Bằng chứng 1: Bản chụp JSON Schema thực tế được truyền vào mảng `tools` trong API request gửi tới mô hình tại lượt chạy đó. Cần kiểm tra xem trong schema gửi đi, tên trường đang được định nghĩa là `course` hay `course_code` (liệu có phải do backend vô tình gửi schema sai tên trường cho LLM hay không).
+- Bằng chứng 2: Toàn bộ nội dung System Prompt và các ví dụ Few-shot trong context. Cần kiểm tra xem có ví dụ cũ hoặc câu chỉ thị nào hướng dẫn gọi hàm dưới dạng `course='...'` khiến mô hình bị học vẹt hay không.
+- Bằng chứng 3: Nếu schema gửi đi ghi rõ `course_code` và không có prompt bias, thì đây là lỗi suy luận của mô hình (Model Extraction Hallucination), cần khắc phục bằng Pydantic Strict Mode trong Structured Outputs.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kỹ thuật Failure Layer Localization yêu cầu phân định rạch ròi giữa 3 lớp: Lớp ứng dụng/Backend (đã pass khi gọi trực tiếp), Lớp trích xuất dữ liệu của Mô hình (đã lấy đúng CS101), và Lớp giao tiếp định dạng/Schema (sinh sai tên khóa `course` vs `course_code`). Không được vội vàng kết luận mô hình kém trước khi kiểm tra schema thực tế mà mô hình nhìn thấy.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenAI Function Calling Debugging Guide &amp; Distributed Tracing Principles in AI Systems (https://platform.openai.com/docs/guides/function-calling)</t>
         </is>
       </c>
     </row>
@@ -860,10 +872,24 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một quyết định cần cả chỉ số lẫn ngưỡng chấp nhận.
-Phân tích theo nguyên lý thiết kế: Một quyết định cần cả chỉ số lẫn ngưỡng chấp nhận.</t>
+- 1.0 điểm: Đưa ra quyết định Điều tra thêm / Tạm dừng rollout v3 một cách có trách nhiệm.
+- 1.0 điểm: Phân tích sâu sắc sự bất ổn định qua độ chênh lệch 88% vs 74% giữa 2 lần chạy lặp.
+- 1.0 điểm: Đánh giá đúng rủi ro tài chính khi chi phí tăng 3 lần trong khi thiếu ngưỡng trần ngân sách.
+- 1.0 điểm: Đề xuất đầy đủ các bằng chứng cần bổ sung (tăng N lần chạy, phân tích trace token, thiết lập cost threshold).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Quyết định: ĐIỀU TRA THÊM (INVESTIGATE FURTHER) và TẠM DỪNG ROLLOUT v3 (giữ v2 trên production).
+2. Lý do căn cứ trên số liệu:
+- Tính bất định và biến động quá cao (High Variance): Hai lần chạy lặp lại cho kết quả chênh lệch nghiêm trọng (88% vs 74%, biên độ dao động 14%). Một hệ thống có phương sai lớn như vậy cho thấy tính năng chưa đạt trạng thái ổn định xác định.
+- Chi phí tăng gấp 3 lần (3x Cost) trong khi chưa có Business Constraint: Sản phẩm chưa xác định ngưỡng trần chi phí cho phép (Cost Ceiling). Việc triển khai một phiên bản tăng chi phí 300% mà không có thỏa thuận SLA về chi phí là rủi ro tài chính lớn cho doanh nghiệp.
+- Độ chính xác tổng thể chưa được chứng minh vượt trội: Nếu lấy trung bình hai lần chạy (88% + 74%) / 2 = 81%, mức cải thiện so với 70% của v2 là có, nhưng chưa đủ bù đắp mức chi phí tăng 300% và độ bất ổn định.
+3. Các bằng chứng cần bổ sung trước khi ra quyết định cuối cùng:
+- Mở rộng số lượng lần chạy đánh giá (N &gt;= 10 lần) trên cùng một bộ test cố định để tính khoảng tin cậy 95% (Confidence Interval) của độ chính xác định tuyến.
+- Phân tích chi tiết Token Usage Trace để tìm hiểu chính xác vì sao chi phí tăng 3 lần (do prompt dài hơn, dùng model đắt hơn hay do vòng lặp retry quá nhiều).
+- Thống nhất với Product Owner và Finance để ban hành Ngưỡng chấp nhận chi phí tối đa (Cost Budget per Request) cho tính năng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một quyết định phát hành trong kỹ thuật phần mềm AI không chỉ dựa vào chỉ số đỉnh (peak metric) trong điều kiện lý tưởng mà phải dựa trên tính ổn định lặp lại (reproducibility) và tính bền vững kinh tế (economic viability). Khi phát hiện biến động mạnh và chi phí tăng vọt không kiểm soát, quyết định an toàn nhất là điều tra nguyên nhân trước khi đưa vào sản xuất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Handbook - Canary Deployments &amp; Release Decisions &amp; Enterprise AI Cost Governance (https://sre.google/sre-book/table-of-contents/)</t>
         </is>
       </c>
     </row>
@@ -947,10 +973,25 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So sánh danh tính trước, rồi mới so sánh hành vi.
-Phân tích theo nguyên lý thiết kế: So sánh danh tính trước, rồi mới so sánh hành vi.</t>
+- 1.0 điểm: Kiểm tra mã băm nội dung thực tế của prompt v4 (chống trôi nhãn phiên bản).
+- 1.0 điểm: Kiểm tra tính đồng nhất của bộ test `cases=base` giữa hai lần chạy.
+- 1.0 điểm: Kiểm tra phiên bản snapshot của model và các siêu tham số suy luận (temperature, seed).
+- 1.0 điểm: Kiểm tra tính ổn định của môi trường tools/backend và tuân thủ đúng trình tự 'so sánh danh tính trước, so sánh hành vi sau'.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Trình tự 4 bước kiểm tra tính so sánh được giữa Lần chạy A và Lần chạy B:
+1. Bước 1: Kiểm tra tính đồng nhất của Nội dung Prompt (Prompt Content Hash Verification)
+- Đối chiếu mã băm SHA-256 của toàn bộ chuỗi system prompt, user template và few-shot examples giữa hai lần chạy. Dù cả hai cùng dán nhãn 'v4', nội dung có thể đã bị chỉnh sửa cục bộ mà không nâng số phiên bản.
+2. Bước 2: Kiểm tra tính đồng nhất của Bộ dữ liệu kiểm thử (Evaluation Dataset Parity)
+- So sánh mã hash hoặc kiểm tra từng bản ghi của bộ test `cases=base`. Cần xác minh xem danh sách câu hỏi, thứ tự xuất hiện, và kỳ vọng chấm điểm của bộ test tại thời điểm chạy A có bị thêm/bớt/sửa đổi khi chạy B hay không.
+3. Bước 3: Kiểm tra Cấu hình Mô hình và Siêu tham số (Model Snapshot &amp; Inference Hyperparameters)
+- Xác minh xem mô hình có bị thay đổi ngầm từ nhà cung cấp hay không (kiểm tra exact model snapshot ID, ví dụ `gpt-4o-2024-05-13` vs `gpt-4o-2024-08-06`).
+- Kiểm tra các tham số `temperature` (nếu temperature &gt; 0 sẽ gây biến thiên kết quả ngẫu nhiên), `seed`, `top_p`, `max_tokens`.
+4. Bước 4: Kiểm tra Phiên bản Công cụ và Môi trường phụ thuộc (Tool Registry &amp; Mock Environment)
+- Xác minh xem schema của các tools được gắn kèm hoặc kết quả trả về từ các mock services/backend có bị thay đổi giữa hai thời điểm chạy hay không. Chỉ khi 4 bước kiểm tra định danh trên đều đồng nhất, sự chênh lệch điểm (9/10 vs 6/10) mới thực sự phản ánh tính bất định nội tại của mô hình.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Theo nguyên tắc Eval Run Artifact Traceability: 'So sánh danh tính trước, so sánh hành vi sau'. Một nhãn tên gọi chung chung như `prompt=v4` không đảm bảo tính đồng nhất nếu thiếu mã băm (content hash). Quy trình kiểm tra tuần tự từ prompt hash, test set, snapshot model tới tool schema là bắt buộc để đảm bảo tính hợp lệ khoa học của thử nghiệm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+MLOps Evaluation &amp; Reproducibility Guidelines (MLflow / Weights &amp; Biases) &amp; NIST AI Standards (https://www.nist.gov/itl/ai-risk-management-framework)</t>
         </is>
       </c>
     </row>
@@ -1035,10 +1076,28 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tổng các nhóm trước khi tính độ chính xác.
-Phân tích theo nguyên lý thiết kế: Kiểm tổng các nhóm trước khi tính độ chính xác.</t>
+- 1.0 điểm: Báo cáo đúng mẫu số đánh giá hành vi là 15 (12 pass / 3 fail = 80%).
+- 1.0 điểm: Tách bạch rõ 5 case lỗi 401 là lỗi hạ tầng xác thực (25%), không gộp bừa vào lỗi mô hình.
+- 1.0 điểm: Trình bày báo cáo trung thực, không phóng đại độ chính xác (phân biệt Behavioral Rate 80% vs E2E Rate 60%).
+- 1.0 điểm: Xác định đúng phạm vi chạy lại: preflight check API token và chỉ chạy lại 5 case lỗi kết nối.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Báo cáo Mẫu số đúng và Phân loại số liệu đánh giá (Không phóng đại độ chính xác):
+- Mẫu số đánh giá hành vi hợp lệ (Valid Behavioral Denominator) = 15 cases (những case thực sự nhận được phản hồi từ mô hình để đánh giá logic).
+  + Số case đạt chuẩn hành vi: 12 cases.
+  + Số case lỗi hành vi (chọn sai tool): 3 cases.
+  + Độ chính xác hành vi (Behavioral Accuracy) = 12 / 15 = 80.0%.
+- Số liệu lỗi hạ tầng nhà cung cấp (Provider Infrastructure Failure):
+  + Số case lỗi 401 Unauthorized: 5 cases.
+  + Tỷ lệ lỗi hạ tầng trước khi đánh giá = 5 / 20 = 25.0%.
+- Tỷ lệ hoàn thành toàn diện (End-to-End Success Rate) = 12 / 20 = 60.0%.
+- Cảnh báo trung thực: Tuyệt đối không báo cáo 12/12 = 100% (bỏ qua 3 case chọn sai tool), và không được lấy 12/20 = 60% làm 'độ chính xác hành vi của mô hình' vì 5 case lỗi 401 là do tầng xác thực API key/hạ tầng chứ không phải do mô hình suy luận sai.
+2. Phạm vi chạy lại (Rerun Scope):
+- Thực hiện bước Preflight Check trước: Kiểm tra tính hợp lệ của API Key/Token và kết nối tới Provider để đảm bảo không còn lỗi 401.
+- Sau khi Preflight pass, chỉ cần chạy lại đúng 5 case bị lỗi 401 để thu thập phản hồi của mô hình và tính toán lại bộ chỉ số trên toàn bộ 20 case.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Provider Preflight Separation yêu cầu phân biệt rạch ròi giữa lỗi kết nối/xác thực hạ tầng (Infrastructure Preflight Error) và lỗi suy luận của mô hình (Model Behavioral Defect). Báo cáo kiểm thử trung thực phải công bố riêng biệt cả hai tỷ lệ này để tránh gây hiểu lầm về năng lực thực tế của mô hình.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google Testing Blog - Test Categorization &amp; Error Budgets &amp; IEEE Standard for Software Test Documentation (https://www.nist.gov/itl/ai-risk-management-framework)</t>
         </is>
       </c>
     </row>
@@ -1118,10 +1177,24 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tính ổn định cần bằng chứng lặp lại trên cùng contract.
-Phân tích theo nguyên lý thiết kế: Tính ổn định cần bằng chứng lặp lại trên cùng contract.</t>
+- 1.0 điểm: Đưa ra kết luận cân bằng: công nhận mock pass 30 đường đi chứng minh logic code chuẩn xác.
+- 1.0 điểm: Chỉ ra dứt khoát việc model thật chỉ chạy 1 lần là chưa đủ bằng chứng để khẳng định tính ổn định.
+- 1.0 điểm: Thiết kế bài test lặp lại (N &gt;= 10 lần) trên mô hình thật để đo độ phân tán và tỷ lệ nhất quán.
+- 1.0 điểm: Bổ sung bài test biến thể ngữ nghĩa (paraphrasing) để đo lường độ bền vững định tuyến.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Kết luận cân bằng về hiện trạng hệ thống:
+'Kết quả kiểm thử cho thấy logic luồng điều khiển, định dạng dữ liệu và các quy tắc nghiệp vụ của đồ thị đã được xác minh toàn diện và hoạt động chính xác trên 30 đường đi mô phỏng (Mock suite pass 100%). Tuy nhiên, việc mô hình thật mới chỉ chạy duy nhất 1 lần và pass KHÔNG ĐỦ CƠ SỞ KHOA HỌC để khẳng định 'agent định tuyến ổn định'. Do tính chất bất định (non-deterministic) của LLM, một mẫu thử N=1 không có ý nghĩa thống kê về khả năng định tuyến ổn định trong môi trường thực tế.'
+2. Thiết kế kiểm tra tiếp theo để kiểm chứng nhận định 'Agent định tuyến ổn định':
+- Kiểm thử lặp lại đo lường độ hội tụ (Repeatability Stress Test):
+  + Chạy mô hình thật lặp lại N &gt;= 10 lần trên toàn bộ 30 tình huống thử nghiệm với các giá trị seed khác nhau.
+  + Đo lường Tỷ lệ định tuyến nhất quán (Consistency Rate) = (Số lần chọn đúng tool dự kiến) / (Tổng số lần chạy).
+- Kiểm thử độ chịu lỗi với biến thể ngôn ngữ (Semantic Robustness Test):
+  + Với mỗi tình huống trong 30 case, tạo ra 3 biến thể diễn đạt khác nhau (paraphrasing: thêm từ lóng, viết tắt, đảo trật tự từ) để kiểm tra xem mô hình có duy trì quyết định gọi đúng công cụ hay bị lệch hướng khi gặp biến thiên ngôn ngữ.
+- Ngưỡng chấp nhận đạt chuẩn: Tỷ lệ định tuyến đúng đạt &gt;= 95% trên toàn bộ các lượt chạy lặp lại.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Mock-Real Evidence Boundary chỉ ra rằng: Mock suite chỉ kiểm tra tính đúng đắn của hợp đồng mã nguồn (Code Contract), còn mô hình AI thật cần bằng chứng thống kê lặp lại (Statistical Evidence) do tính ngẫu nhiên vốn có. Một kỹ sư AI có trách nhiệm không bao giờ quy nạp tính ổn định của agent chỉ từ một lần chạy thành công duy nhất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic Claude Model Evaluation Guidelines &amp; Software Testing Principles for Stochastic Systems (https://docs.anthropic.com/en/docs/build-with-claude/prompt-engineering)</t>
         </is>
       </c>
     </row>
@@ -1206,10 +1279,31 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm soát cứng phải nằm ở nơi thực thi, không chỉ trong văn bản model nhìn thấy.
-Phân tích theo nguyên lý thiết kế: Kiểm soát cứng phải nằm ở nơi thực thi, không chỉ trong văn bản model nhìn thấy.</t>
+- 1.0 điểm: Gán chính xác việc chọn tool refund cho Prompt &amp; Model.
+- 1.0 điểm: Gán chính xác việc kiểm tra tham số order_id/amount cho Tool Contract (JSON Schema/Pydantic).
+- 1.0 điểm: Gán chính xác cổng xác nhận rõ ràng cho Harness Guardrail (không phó mặc cho model).
+- 1.0 điểm: Gán chính xác timeout 5s, retry idempotent và audit tracing cho Harness Middleware.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Ma trận trách nhiệm phân bổ cho luồng Hoàn tiền (Refund Flow):
+1. Nhận diện ý định và Lựa chọn công cụ `refund`:
+- Phân bổ: PROMPT &amp; MODEL (Prompt Instructions &amp; LLM Reasoning).
+- Lý do: Đây là nhiệm vụ hiểu ngôn ngữ tự nhiên, phân tích ý định của khách hàng từ ngữ cảnh trò chuyện để quyết định kích hoạt hành động hoàn tiền.
+2. Ràng buộc đối số bắt buộc phải có `order_id` và `amount` (kiểu dữ liệu và kiểm tra số dương):
+- Phân bổ: CONTRACT CỦA TOOL (Tool JSON Schema &amp; Pydantic Validation Contract).
+- Lý do: Cú pháp, kiểu dữ liệu và danh sách tham số bắt buộc phải được cưỡng chế cứng ở tầng schema định nghĩa công cụ để đảm bảo không bao giờ gọi API khi thiếu dữ liệu đầu vào.
+3. Chốt chặn an toàn: Refund chỉ được thực thi sau khi có xác nhận rõ ràng (Explicit Confirmation):
+- Phân bổ: HARNESS / APPLICATION WORKFLOW (State Machine Guardrail / Human-in-the-loop Gate).
+- Lý do: Đây là kiểm soát an toàn nghiệp vụ (Safety Gate). Tuyệt đối không phó mặc việc xác nhận cho prompt của model; harness phải chặn luồng thực thi, yêu cầu trạng thái `confirmed=True` từ tương tác người dùng mới chuyển sang bước gọi API.
+4. Kiểm soát thời gian chờ (Timeout 5s) và Thử lại 1 lần với Idempotency Key:
+- Phân bổ: HARNESS (Execution Engine / Network Client Middleware).
+- Lý do: Quản lý timeout mạng, retry policy và sinh mã Idempotency Key là trách nhiệm hạ tầng của tầng thực thi (harness), hoàn toàn độc lập với mô hình.
+5. Lưu vết kiểm toán cho mọi sự kiện (Audit Trace):
+- Phân bổ: HARNESS (Observability / Telemetry Middleware).
+- Lý do: Tầng harness tự động ghi nhận mọi sự kiện (lời gọi model, tham số tool, thời gian phản hồi, kết quả) vào hệ thống logging tập trung.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Harness Responsibility Boundary là nguyên lý cốt lõi trong an toàn hệ thống AI: 'Kiểm soát cứng phải nằm ở nơi thực thi (Harness/Code), không được phó mặc cho văn bản mô hình nhìn thấy (Prompt)'. Các chính sách rủi ro cao như hoàn tiền, xác thực OTP, timeout và idempotency bắt buộc phải do Harness và Tool Contract quản lý độc lập.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Principles for Automation &amp; OWASP Top 10 for LLM: LLM08 Excessive Agency Safeguards (https://owasp.org/www-project-top-10-for-large-language-model-applications/)</t>
         </is>
       </c>
     </row>
